--- a/Encollect_Web_DBS_P1/Cypress/fixtures/AllocationToOwner_customeridLevel.xlsx
+++ b/Encollect_Web_DBS_P1/Cypress/fixtures/AllocationToOwner_customeridLevel.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\conta\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Amin\Desktop\DBS\Encollect_Web_DBS_P1 1\Encollect_Web_DBS_P1\Cypress\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEBB29B-970D-4733-942C-FBE5C924DDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>AllocationOwnerCode</t>
   </si>
@@ -47,19 +46,16 @@
     <t>CustomerId</t>
   </si>
   <si>
-    <t>2025-10-10</t>
+    <t>4155</t>
   </si>
   <si>
-    <t>10008932</t>
-  </si>
-  <si>
-    <t>4155</t>
+    <t>2026-10-10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -96,13 +92,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Excel Built-in Normal" xfId="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -414,15 +411,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="30.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="30.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="30.88671875" style="1"/>
-    <col min="4" max="16384" width="30.88671875" style="2"/>
+    <col min="1" max="3" width="30.90625" style="1"/>
+    <col min="4" max="16384" width="30.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -433,15 +430,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>105773000084263</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_DBS_P1/Cypress/fixtures/AllocationToOwner_customeridLevel.xlsx
+++ b/Encollect_Web_DBS_P1/Cypress/fixtures/AllocationToOwner_customeridLevel.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Amin\Desktop\DBS\Encollect_Web_DBS_P1 1\Encollect_Web_DBS_P1\Cypress\fixtures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\conta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEBB29B-970D-4733-942C-FBE5C924DDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>AllocationOwnerCode</t>
   </si>
@@ -46,16 +47,19 @@
     <t>CustomerId</t>
   </si>
   <si>
+    <t>2025-10-10</t>
+  </si>
+  <si>
+    <t>10008932</t>
+  </si>
+  <si>
     <t>4155</t>
-  </si>
-  <si>
-    <t>2026-10-10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -92,14 +96,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Excel Built-in Normal" xfId="1"/>
+    <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -411,15 +414,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="30.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="30.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="30.90625" style="1"/>
-    <col min="4" max="16384" width="30.90625" style="2"/>
+    <col min="1" max="3" width="30.88671875" style="1"/>
+    <col min="4" max="16384" width="30.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -430,15 +433,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
-        <v>105773000084263</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
